--- a/artfynd/A 29975-2024 artfynd.xlsx
+++ b/artfynd/A 29975-2024 artfynd.xlsx
@@ -1994,7 +1994,7 @@
         <v>136242289</v>
       </c>
       <c r="B14" t="n">
-        <v>106517</v>
+        <v>106520</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>136242227</v>
       </c>
       <c r="B16" t="n">
-        <v>107857</v>
+        <v>107860</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>136242236</v>
       </c>
       <c r="B21" t="n">
-        <v>104063</v>
+        <v>104066</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 29975-2024 artfynd.xlsx
+++ b/artfynd/A 29975-2024 artfynd.xlsx
@@ -1994,7 +1994,7 @@
         <v>136242289</v>
       </c>
       <c r="B14" t="n">
-        <v>106520</v>
+        <v>106521</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>136242227</v>
       </c>
       <c r="B16" t="n">
-        <v>107860</v>
+        <v>107861</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>136242236</v>
       </c>
       <c r="B21" t="n">
-        <v>104066</v>
+        <v>104067</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 29975-2024 artfynd.xlsx
+++ b/artfynd/A 29975-2024 artfynd.xlsx
@@ -1994,7 +1994,7 @@
         <v>136242289</v>
       </c>
       <c r="B14" t="n">
-        <v>106521</v>
+        <v>106526</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>136242227</v>
       </c>
       <c r="B16" t="n">
-        <v>107861</v>
+        <v>107866</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>136242236</v>
       </c>
       <c r="B21" t="n">
-        <v>104067</v>
+        <v>104072</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 29975-2024 artfynd.xlsx
+++ b/artfynd/A 29975-2024 artfynd.xlsx
@@ -1994,7 +1994,7 @@
         <v>136242289</v>
       </c>
       <c r="B14" t="n">
-        <v>106526</v>
+        <v>106528</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>136242227</v>
       </c>
       <c r="B16" t="n">
-        <v>107866</v>
+        <v>107868</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>136242236</v>
       </c>
       <c r="B21" t="n">
-        <v>104072</v>
+        <v>104074</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
